--- a/forms/trg/Formulir_TRG_bione-rg.xlsx
+++ b/forms/trg/Formulir_TRG_bione-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B32)</f>
+        <f>COUNTA(Anggota!B5:B33)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F32)</f>
+        <f>COUNTA(Anggota!F5:F33)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ahwiyah Ekawaty Said, S.P., M.Si.</t>
+          <t>Prof. Dr. Ir. Itji Diana Daud, M.S.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Entomology; Biological Control</t>
+          <t>Biological Control and Habitat Management</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,13 +937,13 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7826-2321</t>
+          <t>0000-0002-8990-4086</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57125586100</t>
+          <t>57191167146</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>M. Bayu Mario, S.P., M.P., M.Sc.</t>
+          <t>Ahwiyah Ekawaty Said, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Entomology; Stored-Product Pest; Botanical Pesticide; Insect Taxonomy</t>
+          <t>Entomology; Biological Control</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,13 +982,13 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3619-3348</t>
+          <t>0000-0002-7826-2321</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57206728625</t>
+          <t>57125586100</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Asti Irawanti Azis, S.P., M.Si.</t>
+          <t>M. Bayu Mario, S.P., M.P., M.Sc.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Phytopathology; Nematology</t>
+          <t>Entomology; Stored-Product Pest; Botanical Pesticide; Insect Taxonomy</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1027,11 +1027,15 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1594-7139</t>
+          <t>0000-0002-3619-3348</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57206728625</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1044,12 +1048,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Tutik Kuswinanti, M.Sc.</t>
+          <t>Asti Irawanti Azis, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1059,7 +1063,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Phytopathology; Mycology</t>
+          <t>Phytopathology; Nematology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1068,15 +1072,11 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-1202-3853</t>
+          <t>0000-0002-1594-7139</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>55792741300</t>
-        </is>
-      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1089,22 +1089,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ravindra Chandra Joshi</t>
+          <t>Prof. Dr. Ir. Tutik Kuswinanti, M.Sc.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Philippine Rice Research Institute</t>
+          <t>Faculty of Agriculture, Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Entomology; Integrated Pest Management</t>
+          <t>Phytopathology; Mycology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1113,13 +1113,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6607-4235</t>
+          <t>0009-0005-1202-3853</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>7202085232</t>
+          <t>55792741300</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Lekhnath Kafle</t>
+          <t>Dr. Ravindra Chandra Joshi</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Department of Tropical Agriculture and International Cooperation, National Pingtung University of Science and Technology, Taiwan</t>
+          <t>Philippine Rice Research Institute</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1158,13 +1158,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-5817-9483</t>
+          <t>0000-0002-6607-4235</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>25723335100</t>
+          <t>7202085232</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1179,22 +1179,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Aroua Ammar</t>
+          <t>Dr. Lekhnath Kafle</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Sciences of Sfax, Tunisia</t>
+          <t>Department of Tropical Agriculture and International Cooperation, National Pingtung University of Science and Technology, Taiwan</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Plant Ecophysiology</t>
+          <t>Entomology; Integrated Pest Management</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1203,13 +1203,13 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4733-7108</t>
+          <t>0000-0002-5817-9483</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57211124004</t>
+          <t>25723335100</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1224,22 +1224,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Abdul Fattah, M.P.</t>
+          <t>Dr. Aroua Ammar</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency (BRIN)</t>
+          <t>Faculty of Sciences of Sfax, Tunisia</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Pests and Diseases</t>
+          <t>Plant Ecophysiology</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1248,13 +1248,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6054-5809</t>
+          <t>0000-0002-4733-7108</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>57217829424</t>
+          <t>57211124004</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1269,22 +1269,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. A. Irma Suryani, S.Pd., M.Si.</t>
+          <t>Dr. Ir. Abdul Fattah, M.P.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Mathematics and Natural Sciences, Universitas Negeri Makassar (UNM)</t>
+          <t>National Research and Innovation Agency (BRIN)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Biology; Agricultural Entomology</t>
+          <t>Pests and Diseases</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1293,13 +1293,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7618-3734</t>
+          <t>0000-0002-6054-5809</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>56241700500</t>
+          <t>57217829424</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1314,31 +1314,39 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Mita Yusri, S.P., M.Si.</t>
+          <t>Dr. A. Irma Suryani, S.Pd., M.Si.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Agriculture, Hasanuddin University</t>
+          <t>Faculty of Mathematics and Natural Sciences, Universitas Negeri Makassar (UNM)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Biological Control and Habitat Management</t>
+          <t>Biology; Agricultural Entomology</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-7618-3734</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>56241700500</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1351,12 +1359,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Wardani Syahrani, S.P.</t>
+          <t>Mita Yusri, S.P., M.Si.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1366,7 +1374,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Entomology; Stored-Product Pest</t>
+          <t>Biological Control and Habitat Management</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1375,11 +1383,7 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>58995709300</t>
-        </is>
-      </c>
+      <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1392,12 +1396,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Erna, S.P.</t>
+          <t>Wardani Syahrani, S.P.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1407,7 +1411,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Phytopathology</t>
+          <t>Entomology; Stored-Product Pest</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1416,7 +1420,11 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>58995709300</t>
+        </is>
+      </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1429,12 +1437,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Andi Ince Muhammad Taufan</t>
+          <t>Erna, S.P.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1444,7 +1452,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Entomology</t>
+          <t>Phytopathology</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1466,12 +1474,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Davina Nur Anita</t>
+          <t>Andi Ince Muhammad Taufan</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Phytopathology</t>
+          <t>Entomology</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1503,12 +1511,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Sitti Nurmala Saharuddin</t>
+          <t>Davina Nur Anita</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1540,22 +1548,22 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Anisa Ardani Kalista</t>
+          <t>Sitti Nurmala Saharuddin</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
+          <t>Faculty of Agriculture, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
           <t>Phytopathology</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>BIONE Team</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1575,10 +1583,26 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Anisa Ardani Kalista</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Phytopathology</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>BIONE Team</t>
+        </is>
+      </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
@@ -1586,7 +1610,11 @@
       <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1775,15 +1803,32 @@
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="12" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
